--- a/artfynd/A 68153-2019 artfynd.xlsx
+++ b/artfynd/A 68153-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68153-2019 artfynd.xlsx
+++ b/artfynd/A 68153-2019 artfynd.xlsx
@@ -2068,7 +2068,7 @@
         <v>107606990</v>
       </c>
       <c r="B13" t="n">
-        <v>77595</v>
+        <v>78615</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>687322.234039119</v>
+        <v>687322</v>
       </c>
       <c r="R13" t="n">
-        <v>6608209.622901727</v>
+        <v>6608210</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2185,7 +2185,7 @@
         <v>108132943</v>
       </c>
       <c r="B14" t="n">
-        <v>77595</v>
+        <v>78615</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>687301.9260538928</v>
+        <v>687302</v>
       </c>
       <c r="R14" t="n">
-        <v>6608229.416566079</v>
+        <v>6608229</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>

--- a/artfynd/A 68153-2019 artfynd.xlsx
+++ b/artfynd/A 68153-2019 artfynd.xlsx
@@ -2068,7 +2068,7 @@
         <v>107606990</v>
       </c>
       <c r="B13" t="n">
-        <v>78615</v>
+        <v>78631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>108132943</v>
       </c>
       <c r="B14" t="n">
-        <v>78615</v>
+        <v>78631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
